--- a/namelist_files_and_local_scripts/time_series_station_files_2_dom_all_for_web.xlsx
+++ b/namelist_files_and_local_scripts/time_series_station_files_2_dom_all_for_web.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wjc/GitHub/AES_CEE_Python/Jupyter_Notebooks_and_Other_Files/03_Deep_Dives/03_02_Applications/03_02_05_WRF_and_MPAS_Domain_Mapping/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wjc/GitHub/SD_Mines_WRF_REALTIME/namelist_files_and_local_scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47B030B-132C-FB42-8831-058E08C8F6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24613BEB-6348-344A-BD8E-3A04E221D39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="600" windowWidth="33700" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>Station ID</t>
   </si>
@@ -386,9 +386,6 @@
     <t>Ekalaka Airport, WY</t>
   </si>
   <si>
-    <t>KBHK </t>
-  </si>
-  <si>
     <t>Baker Airport, MT</t>
   </si>
   <si>
@@ -402,6 +399,15 @@
   </si>
   <si>
     <t>Hot Springs Airport, SD</t>
+  </si>
+  <si>
+    <t>KHON</t>
+  </si>
+  <si>
+    <t>Huron Airport, SD</t>
+  </si>
+  <si>
+    <t>KBHK</t>
   </si>
 </sst>
 </file>
@@ -770,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -795,7 +801,6 @@
     </row>
     <row r="2" spans="1:7" ht="19">
       <c r="A2" s="1">
-        <f>1+A1</f>
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -843,7 +848,7 @@
     </row>
     <row r="4" spans="1:7" ht="19">
       <c r="A4" s="1">
-        <f>1+A3</f>
+        <f t="shared" ref="A4:A60" si="0">1+A3</f>
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -867,7 +872,7 @@
     </row>
     <row r="5" spans="1:7" ht="19">
       <c r="A5" s="1">
-        <f>1+A4</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -891,7 +896,8 @@
     </row>
     <row r="6" spans="1:7" ht="19">
       <c r="A6" s="1">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
@@ -914,8 +920,8 @@
     </row>
     <row r="7" spans="1:7" ht="19">
       <c r="A7" s="1">
-        <f>1+A6</f>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
@@ -938,17 +944,17 @@
     </row>
     <row r="8" spans="1:7" ht="19">
       <c r="A8" s="1">
-        <f>1+A7</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="E8" s="1">
         <v>43.884250000000002</v>
@@ -962,8 +968,8 @@
     </row>
     <row r="9" spans="1:7" ht="19">
       <c r="A9" s="1">
-        <f>1+A8</f>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -986,17 +992,17 @@
     </row>
     <row r="10" spans="1:7" ht="19">
       <c r="A10" s="1">
-        <f>1+A9</f>
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="E10" s="4">
         <v>43.368299999999998</v>
@@ -1010,8 +1016,8 @@
     </row>
     <row r="11" spans="1:7" ht="19">
       <c r="A11" s="1">
-        <f>1+A10</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>13</v>
@@ -1034,7 +1040,8 @@
     </row>
     <row r="12" spans="1:7" ht="19">
       <c r="A12" s="1">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>112</v>
@@ -1057,8 +1064,8 @@
     </row>
     <row r="13" spans="1:7" ht="19">
       <c r="A13" s="1">
-        <f>1+A12</f>
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
@@ -1081,8 +1088,8 @@
     </row>
     <row r="14" spans="1:7" ht="19">
       <c r="A14" s="1">
-        <f>1+A13</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>15</v>
@@ -1105,8 +1112,8 @@
     </row>
     <row r="15" spans="1:7" ht="19">
       <c r="A15" s="1">
-        <f>1+A14</f>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>16</v>
@@ -1129,8 +1136,8 @@
     </row>
     <row r="16" spans="1:7" ht="19">
       <c r="A16" s="1">
-        <f>1+A15</f>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>17</v>
@@ -1153,7 +1160,8 @@
     </row>
     <row r="17" spans="1:7" ht="19">
       <c r="A17" s="1">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>18</v>
@@ -1176,8 +1184,8 @@
     </row>
     <row r="18" spans="1:7" ht="19">
       <c r="A18" s="1">
-        <f>1+A17</f>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -1200,7 +1208,8 @@
     </row>
     <row r="19" spans="1:7" ht="19">
       <c r="A19" s="1">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -1223,8 +1232,8 @@
     </row>
     <row r="20" spans="1:7" ht="19">
       <c r="A20" s="1">
-        <f>1+A19</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>21</v>
@@ -1247,7 +1256,8 @@
     </row>
     <row r="21" spans="1:7" ht="19">
       <c r="A21" s="1">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
@@ -1270,7 +1280,8 @@
     </row>
     <row r="22" spans="1:7" ht="19">
       <c r="A22" s="1">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
@@ -1293,8 +1304,8 @@
     </row>
     <row r="23" spans="1:7" ht="19">
       <c r="A23" s="1">
-        <f>1+A22</f>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>24</v>
@@ -1317,7 +1328,8 @@
     </row>
     <row r="24" spans="1:7" ht="19">
       <c r="A24" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>114</v>
@@ -1340,8 +1352,8 @@
     </row>
     <row r="25" spans="1:7" ht="19">
       <c r="A25" s="1">
-        <f>1+A24</f>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>25</v>
@@ -1364,8 +1376,8 @@
     </row>
     <row r="26" spans="1:7" ht="19">
       <c r="A26" s="1">
-        <f>1+A25</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>26</v>
@@ -1388,8 +1400,8 @@
     </row>
     <row r="27" spans="1:7" ht="19">
       <c r="A27" s="1">
-        <f>1+A26</f>
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>27</v>
@@ -1412,8 +1424,8 @@
     </row>
     <row r="28" spans="1:7" ht="19">
       <c r="A28" s="1">
-        <f>1+A27</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
@@ -1436,362 +1448,368 @@
     </row>
     <row r="29" spans="1:7" ht="19">
       <c r="A29" s="1">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1">
-        <v>42.75</v>
+        <v>42.05</v>
       </c>
       <c r="F29" s="1">
-        <v>-105.383</v>
+        <v>-102.8</v>
       </c>
       <c r="G29" s="1">
-        <v>229.35449555827219</v>
+        <v>227.56944345410579</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="19">
       <c r="A30" s="1">
-        <f>1+A29</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30" s="1">
-        <v>46.165500000000002</v>
+        <v>42.75</v>
       </c>
       <c r="F30" s="1">
-        <v>-103.3</v>
+        <v>-105.383</v>
       </c>
       <c r="G30" s="1">
-        <v>232.57826975850921</v>
+        <v>229.35449555827219</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="19">
       <c r="A31" s="1">
-        <f>1+A30</f>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C31" s="1">
         <v>2</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E31" s="1">
-        <v>44.381</v>
+        <v>46.165500000000002</v>
       </c>
       <c r="F31" s="1">
-        <v>-100.286</v>
+        <v>-103.3</v>
       </c>
       <c r="G31" s="1">
-        <v>235.17103910391759</v>
+        <v>232.57826975850921</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="19">
       <c r="A32" s="1">
-        <f>1+A31</f>
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E32" s="1">
-        <v>43.033000000000001</v>
+        <v>42.433</v>
       </c>
       <c r="F32" s="1">
-        <v>-100.617</v>
+        <v>-105.033</v>
       </c>
       <c r="G32" s="1">
-        <v>238.6696483350994</v>
+        <v>234.958321162521</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="19">
       <c r="A33" s="1">
-        <f>1+A32</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C33" s="1">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E33" s="1">
-        <v>42.878</v>
+        <v>44.381</v>
       </c>
       <c r="F33" s="1">
-        <v>-100.55</v>
+        <v>-100.286</v>
       </c>
       <c r="G33" s="1">
-        <v>252.2939738268428</v>
+        <v>235.17103910391759</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="19">
       <c r="A34" s="1">
-        <v>13</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C34" s="3">
-        <v>2</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="3">
-        <v>46.346600000000002</v>
-      </c>
-      <c r="F34" s="3">
-        <v>-104.258</v>
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="1">
+        <v>42.061</v>
+      </c>
+      <c r="F34" s="1">
+        <v>-104.158</v>
       </c>
       <c r="G34" s="1">
-        <v>261.64</v>
+        <v>236.8945391456204</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="19">
       <c r="A35" s="1">
-        <f>1+A34</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C35" s="1">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E35" s="1">
-        <v>45.546300000000002</v>
+        <v>43.033000000000001</v>
       </c>
       <c r="F35" s="1">
-        <v>-100.40600000000001</v>
+        <v>-100.617</v>
       </c>
       <c r="G35" s="1">
-        <v>274.88469192645931</v>
+        <v>238.6696483350994</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="19">
       <c r="A36" s="1">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C36" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E36" s="1">
-        <v>44.986600000000003</v>
+        <v>41.871000000000002</v>
       </c>
       <c r="F36" s="1">
-        <v>-99.9529</v>
+        <v>-103.593</v>
       </c>
       <c r="G36" s="1">
-        <v>277.09447091740418</v>
+        <v>247.07206353589669</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="19">
       <c r="A37" s="1">
-        <f>1+A36</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C37" s="1">
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E37" s="1">
-        <v>46.066899999999997</v>
+        <v>42.878</v>
       </c>
       <c r="F37" s="1">
-        <v>-100.633</v>
+        <v>-100.55</v>
       </c>
       <c r="G37" s="1">
-        <v>299.81103106992452</v>
+        <v>252.2939738268428</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="19">
       <c r="A38" s="1">
-        <v>6</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="1">
-        <v>2</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E38" s="1">
-        <v>46.220599999999997</v>
-      </c>
-      <c r="F38" s="1">
-        <v>-100.246</v>
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" s="3">
+        <v>46.346600000000002</v>
+      </c>
+      <c r="F38" s="3">
+        <v>-104.258</v>
       </c>
       <c r="G38" s="1">
-        <v>332.86743040960818</v>
+        <v>261.64</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="19">
       <c r="A39" s="1">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E39" s="1">
-        <v>42.05</v>
+        <v>45.546300000000002</v>
       </c>
       <c r="F39" s="1">
-        <v>-102.8</v>
+        <v>-100.40600000000001</v>
       </c>
       <c r="G39" s="1">
-        <v>227.56944345410579</v>
+        <v>274.88469192645931</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="19">
       <c r="A40" s="1">
-        <f>1+A39</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C40" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E40" s="1">
-        <v>42.433</v>
+        <v>44.986600000000003</v>
       </c>
       <c r="F40" s="1">
-        <v>-105.033</v>
+        <v>-99.9529</v>
       </c>
       <c r="G40" s="1">
-        <v>234.958321162521</v>
+        <v>277.09447091740418</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="19">
       <c r="A41" s="1">
-        <f>1+A40</f>
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E41" s="1">
-        <v>42.061</v>
+        <v>46.066899999999997</v>
       </c>
       <c r="F41" s="1">
-        <v>-104.158</v>
+        <v>-100.633</v>
       </c>
       <c r="G41" s="1">
-        <v>236.8945391456204</v>
+        <v>299.81103106992452</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="19">
       <c r="A42" s="1">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C42" s="1">
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E42" s="1">
-        <v>41.871000000000002</v>
+        <v>46.7727</v>
       </c>
       <c r="F42" s="1">
-        <v>-103.593</v>
+        <v>-100.746</v>
       </c>
       <c r="G42" s="1">
-        <v>247.07206353589669</v>
+        <v>314.89999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="19">
       <c r="A43" s="1">
-        <f>1+A42</f>
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E43" s="1">
-        <v>46.7727</v>
+        <v>46.220599999999997</v>
       </c>
       <c r="F43" s="1">
-        <v>-100.746</v>
+        <v>-100.246</v>
       </c>
       <c r="G43" s="1">
-        <v>314.89999999999998</v>
+        <v>332.86743040960818</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="19">
       <c r="A44" s="1">
-        <f>1+A43</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>42</v>
@@ -1814,8 +1832,8 @@
     </row>
     <row r="45" spans="1:7" ht="19">
       <c r="A45" s="1">
-        <f>1+A44</f>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>44</v>
@@ -1838,336 +1856,361 @@
     </row>
     <row r="46" spans="1:7" ht="19">
       <c r="A46" s="1">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="C46" s="1">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E46" s="1">
-        <v>45.4467</v>
+        <v>44.385199999999998</v>
       </c>
       <c r="F46" s="1">
-        <v>-98.422399999999996</v>
+        <v>-98.2286</v>
       </c>
       <c r="G46" s="1">
-        <v>407.2835821076373</v>
+        <v>387.7</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="19">
       <c r="A47" s="1">
-        <f>1+A46</f>
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="1">
         <v>1</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E47" s="1">
-        <v>43.0642</v>
+        <v>45.4467</v>
       </c>
       <c r="F47" s="1">
-        <v>-108.46</v>
+        <v>-98.422399999999996</v>
       </c>
       <c r="G47" s="1">
-        <v>437.82235791428252</v>
+        <v>407.2835821076373</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="19">
       <c r="A48" s="1">
-        <f>1+A47</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" s="1">
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E48" s="1">
-        <v>45.7502</v>
+        <v>43.0642</v>
       </c>
       <c r="F48" s="1">
-        <v>-108.57</v>
+        <v>-108.46</v>
       </c>
       <c r="G48" s="1">
-        <v>461.48398607652422</v>
+        <v>437.82235791428252</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="19">
       <c r="A49" s="1">
-        <f>1+A48</f>
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C49" s="1">
         <v>1</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E49" s="1">
-        <v>39.861699999999999</v>
+        <v>45.7502</v>
       </c>
       <c r="F49" s="1">
-        <v>-104.673</v>
+        <v>-108.57</v>
       </c>
       <c r="G49" s="1">
-        <v>483.89787803782338</v>
+        <v>461.48398607652422</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="19">
       <c r="A50" s="1">
-        <f>1+A49</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="1">
         <v>1</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E50" s="1">
-        <v>39.991999999999997</v>
+        <v>39.861699999999999</v>
       </c>
       <c r="F50" s="1">
-        <v>-105.261</v>
+        <v>-104.673</v>
       </c>
       <c r="G50" s="1">
-        <v>484.62654498579639</v>
+        <v>483.89787803782338</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="19">
       <c r="A51" s="1">
-        <f>1+A50</f>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" s="1">
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E51" s="1">
-        <v>43.582000000000001</v>
+        <v>39.991999999999997</v>
       </c>
       <c r="F51" s="1">
-        <v>-96.741900000000001</v>
+        <v>-105.261</v>
       </c>
       <c r="G51" s="1">
-        <v>521.33382524072977</v>
+        <v>484.62654498579639</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="19">
       <c r="A52" s="1">
-        <f>1+A51</f>
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C52" s="1">
         <v>1</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52" s="1">
-        <v>48.212400000000002</v>
+        <v>43.582000000000001</v>
       </c>
       <c r="F52" s="1">
-        <v>-106.61499999999999</v>
+        <v>-96.741900000000001</v>
       </c>
       <c r="G52" s="1">
-        <v>529.60258153152961</v>
+        <v>521.33382524072977</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="19">
       <c r="A53" s="1">
-        <f>1+A52</f>
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E53" s="1">
-        <v>39.370699999999999</v>
+        <v>48.212400000000002</v>
       </c>
       <c r="F53" s="1">
-        <v>-101.699</v>
+        <v>-106.61499999999999</v>
       </c>
       <c r="G53" s="1">
-        <v>537.81299158903198</v>
+        <v>529.60258153152961</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="19">
       <c r="A54" s="1">
-        <f>1+A53</f>
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" s="1">
         <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E54" s="1">
-        <v>40.647500000000001</v>
+        <v>39.370699999999999</v>
       </c>
       <c r="F54" s="1">
-        <v>-98.383700000000005</v>
+        <v>-101.699</v>
       </c>
       <c r="G54" s="1">
-        <v>549.60430011219228</v>
+        <v>537.81299158903198</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="19">
       <c r="A55" s="1">
-        <f>1+A54</f>
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C55" s="1">
         <v>1</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E55" s="1">
-        <v>48.667499999999997</v>
+        <v>40.647500000000001</v>
       </c>
       <c r="F55" s="1">
-        <v>-98.834400000000002</v>
+        <v>-98.383700000000005</v>
       </c>
       <c r="G55" s="1">
-        <v>610.75548649454925</v>
+        <v>549.60430011219228</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="19">
       <c r="A56" s="1">
-        <f>1+A55</f>
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C56" s="1">
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E56" s="1">
-        <v>47.921900000000001</v>
+        <v>48.667499999999997</v>
       </c>
       <c r="F56" s="1">
-        <v>-97.098100000000002</v>
+        <v>-98.834400000000002</v>
       </c>
       <c r="G56" s="1">
-        <v>636.5233353769745</v>
+        <v>610.75548649454925</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="19">
       <c r="A57" s="1">
-        <f>1+A56</f>
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C57" s="1">
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E57" s="1">
-        <v>41.319699999999997</v>
+        <v>47.921900000000001</v>
       </c>
       <c r="F57" s="1">
-        <v>-96.3673</v>
+        <v>-97.098100000000002</v>
       </c>
       <c r="G57" s="1">
-        <v>637.07875462019854</v>
+        <v>636.5233353769745</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="19">
       <c r="A58" s="1">
-        <f>1+A57</f>
-        <v>22</v>
+        <f t="shared" si="0"/>
+        <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C58" s="1">
         <v>1</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E58" s="1">
-        <v>39.122399999999999</v>
+        <v>41.319699999999997</v>
       </c>
       <c r="F58" s="1">
-        <v>-108.527</v>
+        <v>-96.3673</v>
       </c>
       <c r="G58" s="1">
-        <v>706.05970680141979</v>
+        <v>637.07875462019854</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="19">
       <c r="A59" s="1">
-        <f>1+A58</f>
-        <v>23</v>
+        <f t="shared" si="0"/>
+        <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E59" s="1">
+        <v>39.122399999999999</v>
+      </c>
+      <c r="F59" s="1">
+        <v>-108.527</v>
+      </c>
+      <c r="G59" s="1">
+        <v>706.05970680141979</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="19">
+      <c r="A60" s="1">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C59" s="1">
-        <v>1</v>
-      </c>
-      <c r="D59" s="1" t="s">
+      <c r="C60" s="1">
+        <v>1</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E60" s="1">
         <v>39.068800000000003</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F60" s="1">
         <v>-95.622399999999999</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G60" s="1">
         <v>840.71703075227481</v>
       </c>
     </row>
